--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.101735612366437</v>
+        <v>0.8290320370095461</v>
       </c>
       <c r="D2" t="n">
-        <v>5.528939679155116</v>
+        <v>0.8984526978627064</v>
       </c>
       <c r="E2" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F2" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.47220361892622</v>
+        <v>3.164233088075511</v>
       </c>
       <c r="D3" t="n">
-        <v>17.48408565683494</v>
+        <v>2.841163919235678</v>
       </c>
       <c r="E3" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F3" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.47779784088807</v>
+        <v>2.677642149144311</v>
       </c>
       <c r="D4" t="n">
-        <v>16.17684347757874</v>
+        <v>2.628737065106545</v>
       </c>
       <c r="E4" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F4" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.501433677768481</v>
+        <v>0.5689829726373782</v>
       </c>
       <c r="D5" t="n">
-        <v>11.64192369015795</v>
+        <v>1.891812599650667</v>
       </c>
       <c r="E5" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F5" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.95628340734294</v>
+        <v>4.380396053693228</v>
       </c>
       <c r="D6" t="n">
-        <v>26.74645390305996</v>
+        <v>4.346298759247244</v>
       </c>
       <c r="E6" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F6" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.61255885116283</v>
+        <v>5.13704081331396</v>
       </c>
       <c r="D7" t="n">
-        <v>31.27810683599838</v>
+        <v>5.082692360849737</v>
       </c>
       <c r="E7" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F7" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.94534839281688</v>
+        <v>5.841119113832742</v>
       </c>
       <c r="D8" t="n">
-        <v>35.37640174310566</v>
+        <v>5.74866528325467</v>
       </c>
       <c r="E8" t="n">
-        <v>11.61413380052142</v>
+        <v>1.88729674258473</v>
       </c>
       <c r="F8" t="n">
-        <v>10.04845391498114</v>
+        <v>1.632873761184436</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
